--- a/data/positions.xlsx
+++ b/data/positions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="42">
   <si>
     <t>loan_id</t>
   </si>
@@ -64,6 +64,12 @@
     <t>dscr</t>
   </si>
   <si>
+    <t>commitment</t>
+  </si>
+  <si>
+    <t>undrawn</t>
+  </si>
+  <si>
     <t>L001</t>
   </si>
   <si>
@@ -77,9 +83,6 @@
   </si>
   <si>
     <t>L005</t>
-  </si>
-  <si>
-    <t>2024-12-31</t>
   </si>
   <si>
     <t>BB</t>
@@ -143,6 +146,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -195,11 +201,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,10 +501,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -546,69 +553,81 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45322</v>
       </c>
       <c r="C2">
-        <v>25000000</v>
+        <v>20000000</v>
       </c>
       <c r="D2">
-        <v>24850000</v>
+        <v>20000000</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2">
         <v>450</v>
       </c>
       <c r="K2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L2">
-        <v>0.08500000000000001</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="M2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N2">
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="P2">
         <v>1.85</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2">
+        <v>30000000</v>
+      </c>
+      <c r="R2">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45351</v>
       </c>
       <c r="C3">
-        <v>18000000</v>
+        <v>23000000</v>
       </c>
       <c r="D3">
-        <v>17600000</v>
+        <v>23000000</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
@@ -620,175 +639,3213 @@
         <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J3">
-        <v>525</v>
+        <v>450</v>
       </c>
       <c r="K3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L3">
-        <v>0.092</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="M3" t="s">
         <v>40</v>
       </c>
       <c r="N3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="P3">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>1.85</v>
+      </c>
+      <c r="Q3">
+        <v>30000000</v>
+      </c>
+      <c r="R3">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
-        <v>21</v>
+      <c r="B4" s="2">
+        <v>45382</v>
       </c>
       <c r="C4">
-        <v>32000000</v>
+        <v>23000000</v>
       </c>
       <c r="D4">
-        <v>31000000</v>
+        <v>23000000</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
         <v>37</v>
       </c>
       <c r="J4">
-        <v>600</v>
+        <v>450</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
       </c>
       <c r="L4">
-        <v>0.095</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="M4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0.64</v>
+      </c>
+      <c r="P4">
+        <v>1.86</v>
+      </c>
+      <c r="Q4">
+        <v>30000000</v>
+      </c>
+      <c r="R4">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C5">
+        <v>24000000</v>
+      </c>
+      <c r="D5">
+        <v>24000000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5">
+        <v>450</v>
+      </c>
+      <c r="K5" t="s">
         <v>39</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0.58</v>
-      </c>
-      <c r="P4">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5">
-        <v>15000000</v>
-      </c>
-      <c r="D5">
-        <v>14200000</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5">
-        <v>650</v>
-      </c>
-      <c r="K5" t="s">
-        <v>38</v>
-      </c>
       <c r="L5">
-        <v>0.103</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="M5" t="s">
         <v>40</v>
       </c>
       <c r="N5">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="P5">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>1.86</v>
+      </c>
+      <c r="Q5">
+        <v>30000000</v>
+      </c>
+      <c r="R5">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45443</v>
       </c>
       <c r="C6">
-        <v>22000000</v>
+        <v>25000000</v>
       </c>
       <c r="D6">
-        <v>22000000</v>
+        <v>25000000</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
         <v>37</v>
       </c>
       <c r="J6">
+        <v>450</v>
+      </c>
+      <c r="K6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6">
+        <v>0.08499999999999999</v>
+      </c>
+      <c r="M6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0.65</v>
+      </c>
+      <c r="P6">
+        <v>1.87</v>
+      </c>
+      <c r="Q6">
+        <v>30000000</v>
+      </c>
+      <c r="R6">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C7">
+        <v>25000000</v>
+      </c>
+      <c r="D7">
+        <v>25000000</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7">
+        <v>450</v>
+      </c>
+      <c r="K7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7">
+        <v>0.08499999999999999</v>
+      </c>
+      <c r="M7" t="s">
+        <v>40</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0.65</v>
+      </c>
+      <c r="P7">
+        <v>1.88</v>
+      </c>
+      <c r="Q7">
+        <v>30000000</v>
+      </c>
+      <c r="R7">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C8">
+        <v>24800000</v>
+      </c>
+      <c r="D8">
+        <v>24800000</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8">
+        <v>450</v>
+      </c>
+      <c r="K8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8">
+        <v>0.08499999999999999</v>
+      </c>
+      <c r="M8" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0.65</v>
+      </c>
+      <c r="P8">
+        <v>1.9</v>
+      </c>
+      <c r="Q8">
+        <v>30000000</v>
+      </c>
+      <c r="R8">
+        <v>5200000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C9">
+        <v>24600000</v>
+      </c>
+      <c r="D9">
+        <v>24600000</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9">
+        <v>450</v>
+      </c>
+      <c r="K9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9">
+        <v>0.08499999999999999</v>
+      </c>
+      <c r="M9" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0.64</v>
+      </c>
+      <c r="P9">
+        <v>1.91</v>
+      </c>
+      <c r="Q9">
+        <v>30000000</v>
+      </c>
+      <c r="R9">
+        <v>5400000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C10">
+        <v>24400000</v>
+      </c>
+      <c r="D10">
+        <v>24400000</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10">
+        <v>450</v>
+      </c>
+      <c r="K10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10">
+        <v>0.08499999999999999</v>
+      </c>
+      <c r="M10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0.64</v>
+      </c>
+      <c r="P10">
+        <v>1.92</v>
+      </c>
+      <c r="Q10">
+        <v>30000000</v>
+      </c>
+      <c r="R10">
+        <v>5600000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C11">
+        <v>23200000</v>
+      </c>
+      <c r="D11">
+        <v>23200000</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11">
+        <v>450</v>
+      </c>
+      <c r="K11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11">
+        <v>0.08499999999999999</v>
+      </c>
+      <c r="M11" t="s">
+        <v>40</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0.63</v>
+      </c>
+      <c r="P11">
+        <v>1.93</v>
+      </c>
+      <c r="Q11">
+        <v>30000000</v>
+      </c>
+      <c r="R11">
+        <v>6800000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C12">
+        <v>23000000</v>
+      </c>
+      <c r="D12">
+        <v>23000000</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12">
+        <v>450</v>
+      </c>
+      <c r="K12" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12">
+        <v>0.08499999999999999</v>
+      </c>
+      <c r="M12" t="s">
+        <v>40</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0.63</v>
+      </c>
+      <c r="P12">
+        <v>1.94</v>
+      </c>
+      <c r="Q12">
+        <v>30000000</v>
+      </c>
+      <c r="R12">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C13">
+        <v>22800000</v>
+      </c>
+      <c r="D13">
+        <v>22800000</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13">
+        <v>450</v>
+      </c>
+      <c r="K13" t="s">
+        <v>39</v>
+      </c>
+      <c r="L13">
+        <v>0.08499999999999999</v>
+      </c>
+      <c r="M13" t="s">
+        <v>40</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0.62</v>
+      </c>
+      <c r="P13">
+        <v>1.95</v>
+      </c>
+      <c r="Q13">
+        <v>30000000</v>
+      </c>
+      <c r="R13">
+        <v>7200000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="2">
+        <v>45322</v>
+      </c>
+      <c r="C14">
+        <v>13000000</v>
+      </c>
+      <c r="D14">
+        <v>13000000</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14">
+        <v>525</v>
+      </c>
+      <c r="K14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L14">
+        <v>0.0925</v>
+      </c>
+      <c r="M14" t="s">
+        <v>40</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0.7</v>
+      </c>
+      <c r="P14">
+        <v>1.5</v>
+      </c>
+      <c r="Q14">
+        <v>25000000</v>
+      </c>
+      <c r="R14">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="2">
+        <v>45351</v>
+      </c>
+      <c r="C15">
+        <v>13000000</v>
+      </c>
+      <c r="D15">
+        <v>13000000</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15">
+        <v>525</v>
+      </c>
+      <c r="K15" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15">
+        <v>0.0925</v>
+      </c>
+      <c r="M15" t="s">
+        <v>40</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0.71</v>
+      </c>
+      <c r="P15">
+        <v>1.5</v>
+      </c>
+      <c r="Q15">
+        <v>25000000</v>
+      </c>
+      <c r="R15">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="2">
+        <v>45382</v>
+      </c>
+      <c r="C16">
+        <v>16000000</v>
+      </c>
+      <c r="D16">
+        <v>16000000</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16">
+        <v>525</v>
+      </c>
+      <c r="K16" t="s">
+        <v>39</v>
+      </c>
+      <c r="L16">
+        <v>0.0925</v>
+      </c>
+      <c r="M16" t="s">
+        <v>40</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0.71</v>
+      </c>
+      <c r="P16">
+        <v>1.51</v>
+      </c>
+      <c r="Q16">
+        <v>25000000</v>
+      </c>
+      <c r="R16">
+        <v>9000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C17">
+        <v>16000000</v>
+      </c>
+      <c r="D17">
+        <v>16000000</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17">
+        <v>525</v>
+      </c>
+      <c r="K17" t="s">
+        <v>39</v>
+      </c>
+      <c r="L17">
+        <v>0.0925</v>
+      </c>
+      <c r="M17" t="s">
+        <v>40</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0.72</v>
+      </c>
+      <c r="P17">
+        <v>1.51</v>
+      </c>
+      <c r="Q17">
+        <v>25000000</v>
+      </c>
+      <c r="R17">
+        <v>9000000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C18">
+        <v>18000000</v>
+      </c>
+      <c r="D18">
+        <v>18000000</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18">
+        <v>525</v>
+      </c>
+      <c r="K18" t="s">
+        <v>39</v>
+      </c>
+      <c r="L18">
+        <v>0.0925</v>
+      </c>
+      <c r="M18" t="s">
+        <v>40</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0.72</v>
+      </c>
+      <c r="P18">
+        <v>1.52</v>
+      </c>
+      <c r="Q18">
+        <v>25000000</v>
+      </c>
+      <c r="R18">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C19">
+        <v>18060000</v>
+      </c>
+      <c r="D19">
+        <v>17518200</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" t="s">
+        <v>37</v>
+      </c>
+      <c r="J19">
+        <v>525</v>
+      </c>
+      <c r="K19" t="s">
+        <v>39</v>
+      </c>
+      <c r="L19">
+        <v>0.0925</v>
+      </c>
+      <c r="M19" t="s">
+        <v>41</v>
+      </c>
+      <c r="N19">
+        <v>15</v>
+      </c>
+      <c r="O19">
+        <v>0.72</v>
+      </c>
+      <c r="P19">
+        <v>1.53</v>
+      </c>
+      <c r="Q19">
+        <v>25000000</v>
+      </c>
+      <c r="R19">
+        <v>6940000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C20">
+        <v>18120000</v>
+      </c>
+      <c r="D20">
+        <v>17576400</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" t="s">
+        <v>37</v>
+      </c>
+      <c r="J20">
+        <v>525</v>
+      </c>
+      <c r="K20" t="s">
+        <v>39</v>
+      </c>
+      <c r="L20">
+        <v>0.0925</v>
+      </c>
+      <c r="M20" t="s">
+        <v>41</v>
+      </c>
+      <c r="N20">
+        <v>15</v>
+      </c>
+      <c r="O20">
+        <v>0.72</v>
+      </c>
+      <c r="P20">
+        <v>1.55</v>
+      </c>
+      <c r="Q20">
+        <v>25000000</v>
+      </c>
+      <c r="R20">
+        <v>6880000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C21">
+        <v>18030000</v>
+      </c>
+      <c r="D21">
+        <v>17489100</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21">
+        <v>525</v>
+      </c>
+      <c r="K21" t="s">
+        <v>39</v>
+      </c>
+      <c r="L21">
+        <v>0.0925</v>
+      </c>
+      <c r="M21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N21">
+        <v>15</v>
+      </c>
+      <c r="O21">
+        <v>0.71</v>
+      </c>
+      <c r="P21">
+        <v>1.56</v>
+      </c>
+      <c r="Q21">
+        <v>25000000</v>
+      </c>
+      <c r="R21">
+        <v>6970000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C22">
+        <v>17880000</v>
+      </c>
+      <c r="D22">
+        <v>17880000</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22">
+        <v>525</v>
+      </c>
+      <c r="K22" t="s">
+        <v>39</v>
+      </c>
+      <c r="L22">
+        <v>0.0925</v>
+      </c>
+      <c r="M22" t="s">
+        <v>40</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0.71</v>
+      </c>
+      <c r="P22">
+        <v>1.57</v>
+      </c>
+      <c r="Q22">
+        <v>25000000</v>
+      </c>
+      <c r="R22">
+        <v>7120000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C23">
+        <v>17730000</v>
+      </c>
+      <c r="D23">
+        <v>17730000</v>
+      </c>
+      <c r="E23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23">
+        <v>525</v>
+      </c>
+      <c r="K23" t="s">
+        <v>39</v>
+      </c>
+      <c r="L23">
+        <v>0.0925</v>
+      </c>
+      <c r="M23" t="s">
+        <v>40</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0.7</v>
+      </c>
+      <c r="P23">
+        <v>1.58</v>
+      </c>
+      <c r="Q23">
+        <v>25000000</v>
+      </c>
+      <c r="R23">
+        <v>7270000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C24">
+        <v>17580000</v>
+      </c>
+      <c r="D24">
+        <v>17580000</v>
+      </c>
+      <c r="E24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" t="s">
+        <v>36</v>
+      </c>
+      <c r="I24" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24">
+        <v>525</v>
+      </c>
+      <c r="K24" t="s">
+        <v>39</v>
+      </c>
+      <c r="L24">
+        <v>0.0925</v>
+      </c>
+      <c r="M24" t="s">
+        <v>40</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0.7</v>
+      </c>
+      <c r="P24">
+        <v>1.59</v>
+      </c>
+      <c r="Q24">
+        <v>25000000</v>
+      </c>
+      <c r="R24">
+        <v>7420000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C25">
+        <v>16930000</v>
+      </c>
+      <c r="D25">
+        <v>16930000</v>
+      </c>
+      <c r="E25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" t="s">
+        <v>37</v>
+      </c>
+      <c r="J25">
+        <v>525</v>
+      </c>
+      <c r="K25" t="s">
+        <v>39</v>
+      </c>
+      <c r="L25">
+        <v>0.0925</v>
+      </c>
+      <c r="M25" t="s">
+        <v>40</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P25">
+        <v>1.6</v>
+      </c>
+      <c r="Q25">
+        <v>25000000</v>
+      </c>
+      <c r="R25">
+        <v>8070000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="2">
+        <v>45322</v>
+      </c>
+      <c r="C26">
+        <v>31500000</v>
+      </c>
+      <c r="D26">
+        <v>31027500</v>
+      </c>
+      <c r="E26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26">
+        <v>600</v>
+      </c>
+      <c r="L26">
+        <v>0.095</v>
+      </c>
+      <c r="M26" t="s">
+        <v>40</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0.6</v>
+      </c>
+      <c r="P26">
+        <v>2.15</v>
+      </c>
+      <c r="Q26">
+        <v>32000000</v>
+      </c>
+      <c r="R26">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="2">
+        <v>45351</v>
+      </c>
+      <c r="C27">
+        <v>31000000</v>
+      </c>
+      <c r="D27">
+        <v>30535000</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" t="s">
+        <v>36</v>
+      </c>
+      <c r="I27" t="s">
+        <v>38</v>
+      </c>
+      <c r="J27">
+        <v>600</v>
+      </c>
+      <c r="L27">
+        <v>0.095</v>
+      </c>
+      <c r="M27" t="s">
+        <v>40</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0.61</v>
+      </c>
+      <c r="P27">
+        <v>2.15</v>
+      </c>
+      <c r="Q27">
+        <v>32000000</v>
+      </c>
+      <c r="R27">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="2">
+        <v>45382</v>
+      </c>
+      <c r="C28">
+        <v>30500000</v>
+      </c>
+      <c r="D28">
+        <v>30042500</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" t="s">
+        <v>36</v>
+      </c>
+      <c r="I28" t="s">
+        <v>38</v>
+      </c>
+      <c r="J28">
+        <v>600</v>
+      </c>
+      <c r="L28">
+        <v>0.095</v>
+      </c>
+      <c r="M28" t="s">
+        <v>40</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0.61</v>
+      </c>
+      <c r="P28">
+        <v>2.16</v>
+      </c>
+      <c r="Q28">
+        <v>32000000</v>
+      </c>
+      <c r="R28">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C29">
+        <v>30000000</v>
+      </c>
+      <c r="D29">
+        <v>29550000</v>
+      </c>
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" t="s">
+        <v>38</v>
+      </c>
+      <c r="J29">
+        <v>600</v>
+      </c>
+      <c r="L29">
+        <v>0.095</v>
+      </c>
+      <c r="M29" t="s">
+        <v>40</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0.62</v>
+      </c>
+      <c r="P29">
+        <v>2.16</v>
+      </c>
+      <c r="Q29">
+        <v>32000000</v>
+      </c>
+      <c r="R29">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C30">
+        <v>29500000</v>
+      </c>
+      <c r="D30">
+        <v>29057500</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30" t="s">
+        <v>38</v>
+      </c>
+      <c r="J30">
+        <v>600</v>
+      </c>
+      <c r="L30">
+        <v>0.095</v>
+      </c>
+      <c r="M30" t="s">
+        <v>40</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0.62</v>
+      </c>
+      <c r="P30">
+        <v>2.17</v>
+      </c>
+      <c r="Q30">
+        <v>32000000</v>
+      </c>
+      <c r="R30">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C31">
+        <v>29000000</v>
+      </c>
+      <c r="D31">
+        <v>28565000</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31" t="s">
+        <v>38</v>
+      </c>
+      <c r="J31">
+        <v>600</v>
+      </c>
+      <c r="L31">
+        <v>0.095</v>
+      </c>
+      <c r="M31" t="s">
+        <v>40</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0.62</v>
+      </c>
+      <c r="P31">
+        <v>2.18</v>
+      </c>
+      <c r="Q31">
+        <v>32000000</v>
+      </c>
+      <c r="R31">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C32">
+        <v>28500000</v>
+      </c>
+      <c r="D32">
+        <v>28072500</v>
+      </c>
+      <c r="E32" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" t="s">
+        <v>33</v>
+      </c>
+      <c r="H32" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32" t="s">
+        <v>38</v>
+      </c>
+      <c r="J32">
+        <v>600</v>
+      </c>
+      <c r="L32">
+        <v>0.095</v>
+      </c>
+      <c r="M32" t="s">
+        <v>40</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0.62</v>
+      </c>
+      <c r="P32">
+        <v>2.2</v>
+      </c>
+      <c r="Q32">
+        <v>32000000</v>
+      </c>
+      <c r="R32">
+        <v>3500000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C33">
+        <v>28000000</v>
+      </c>
+      <c r="D33">
+        <v>27580000</v>
+      </c>
+      <c r="E33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" t="s">
+        <v>33</v>
+      </c>
+      <c r="H33" t="s">
+        <v>36</v>
+      </c>
+      <c r="I33" t="s">
+        <v>38</v>
+      </c>
+      <c r="J33">
+        <v>600</v>
+      </c>
+      <c r="L33">
+        <v>0.095</v>
+      </c>
+      <c r="M33" t="s">
+        <v>40</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0.61</v>
+      </c>
+      <c r="P33">
+        <v>2.21</v>
+      </c>
+      <c r="Q33">
+        <v>32000000</v>
+      </c>
+      <c r="R33">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C34">
+        <v>26000000</v>
+      </c>
+      <c r="D34">
+        <v>25610000</v>
+      </c>
+      <c r="E34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" t="s">
+        <v>33</v>
+      </c>
+      <c r="H34" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" t="s">
+        <v>38</v>
+      </c>
+      <c r="J34">
+        <v>600</v>
+      </c>
+      <c r="L34">
+        <v>0.095</v>
+      </c>
+      <c r="M34" t="s">
+        <v>40</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0.61</v>
+      </c>
+      <c r="P34">
+        <v>2.22</v>
+      </c>
+      <c r="Q34">
+        <v>32000000</v>
+      </c>
+      <c r="R34">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C35">
+        <v>25500000</v>
+      </c>
+      <c r="D35">
+        <v>25117500</v>
+      </c>
+      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" t="s">
+        <v>38</v>
+      </c>
+      <c r="J35">
+        <v>600</v>
+      </c>
+      <c r="L35">
+        <v>0.095</v>
+      </c>
+      <c r="M35" t="s">
+        <v>40</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0.6</v>
+      </c>
+      <c r="P35">
+        <v>2.23</v>
+      </c>
+      <c r="Q35">
+        <v>32000000</v>
+      </c>
+      <c r="R35">
+        <v>6500000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C36">
+        <v>25000000</v>
+      </c>
+      <c r="D36">
+        <v>24625000</v>
+      </c>
+      <c r="E36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" t="s">
+        <v>33</v>
+      </c>
+      <c r="H36" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36" t="s">
+        <v>38</v>
+      </c>
+      <c r="J36">
+        <v>600</v>
+      </c>
+      <c r="L36">
+        <v>0.095</v>
+      </c>
+      <c r="M36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0.6</v>
+      </c>
+      <c r="P36">
+        <v>2.24</v>
+      </c>
+      <c r="Q36">
+        <v>32000000</v>
+      </c>
+      <c r="R36">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C37">
+        <v>24500000</v>
+      </c>
+      <c r="D37">
+        <v>24132500</v>
+      </c>
+      <c r="E37" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" t="s">
+        <v>33</v>
+      </c>
+      <c r="H37" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" t="s">
+        <v>38</v>
+      </c>
+      <c r="J37">
+        <v>600</v>
+      </c>
+      <c r="L37">
+        <v>0.095</v>
+      </c>
+      <c r="M37" t="s">
+        <v>40</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0.59</v>
+      </c>
+      <c r="P37">
+        <v>2.25</v>
+      </c>
+      <c r="Q37">
+        <v>32000000</v>
+      </c>
+      <c r="R37">
+        <v>7500000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="C38">
+        <v>8000000</v>
+      </c>
+      <c r="D38">
+        <v>8000000</v>
+      </c>
+      <c r="E38" t="s">
+        <v>26</v>
+      </c>
+      <c r="F38" t="s">
+        <v>30</v>
+      </c>
+      <c r="G38" t="s">
+        <v>34</v>
+      </c>
+      <c r="H38" t="s">
+        <v>36</v>
+      </c>
+      <c r="I38" t="s">
+        <v>37</v>
+      </c>
+      <c r="J38">
+        <v>650</v>
+      </c>
+      <c r="K38" t="s">
+        <v>39</v>
+      </c>
+      <c r="L38">
+        <v>0.105</v>
+      </c>
+      <c r="M38" t="s">
+        <v>40</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0.76</v>
+      </c>
+      <c r="P38">
+        <v>1.25</v>
+      </c>
+      <c r="Q38">
+        <v>20000000</v>
+      </c>
+      <c r="R38">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="2">
+        <v>45351</v>
+      </c>
+      <c r="C39">
+        <v>10000000</v>
+      </c>
+      <c r="D39">
+        <v>10000000</v>
+      </c>
+      <c r="E39" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" t="s">
+        <v>30</v>
+      </c>
+      <c r="G39" t="s">
+        <v>34</v>
+      </c>
+      <c r="H39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I39" t="s">
+        <v>37</v>
+      </c>
+      <c r="J39">
+        <v>650</v>
+      </c>
+      <c r="K39" t="s">
+        <v>39</v>
+      </c>
+      <c r="L39">
+        <v>0.105</v>
+      </c>
+      <c r="M39" t="s">
+        <v>40</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0.77</v>
+      </c>
+      <c r="P39">
+        <v>1.22</v>
+      </c>
+      <c r="Q39">
+        <v>20000000</v>
+      </c>
+      <c r="R39">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="2">
+        <v>45382</v>
+      </c>
+      <c r="C40">
+        <v>12000000</v>
+      </c>
+      <c r="D40">
+        <v>12000000</v>
+      </c>
+      <c r="E40" t="s">
+        <v>26</v>
+      </c>
+      <c r="F40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" t="s">
+        <v>36</v>
+      </c>
+      <c r="I40" t="s">
+        <v>37</v>
+      </c>
+      <c r="J40">
+        <v>650</v>
+      </c>
+      <c r="K40" t="s">
+        <v>39</v>
+      </c>
+      <c r="L40">
+        <v>0.105</v>
+      </c>
+      <c r="M40" t="s">
+        <v>40</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0.78</v>
+      </c>
+      <c r="P40">
+        <v>1.19</v>
+      </c>
+      <c r="Q40">
+        <v>20000000</v>
+      </c>
+      <c r="R40">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C41">
+        <v>12000000</v>
+      </c>
+      <c r="D41">
+        <v>12000000</v>
+      </c>
+      <c r="E41" t="s">
+        <v>26</v>
+      </c>
+      <c r="F41" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" t="s">
+        <v>36</v>
+      </c>
+      <c r="I41" t="s">
+        <v>37</v>
+      </c>
+      <c r="J41">
+        <v>650</v>
+      </c>
+      <c r="K41" t="s">
+        <v>39</v>
+      </c>
+      <c r="L41">
+        <v>0.105</v>
+      </c>
+      <c r="M41" t="s">
+        <v>40</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0.79</v>
+      </c>
+      <c r="P41">
+        <v>1.15</v>
+      </c>
+      <c r="Q41">
+        <v>20000000</v>
+      </c>
+      <c r="R41">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C42">
+        <v>12000000</v>
+      </c>
+      <c r="D42">
+        <v>12000000</v>
+      </c>
+      <c r="E42" t="s">
+        <v>26</v>
+      </c>
+      <c r="F42" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" t="s">
+        <v>37</v>
+      </c>
+      <c r="J42">
+        <v>650</v>
+      </c>
+      <c r="K42" t="s">
+        <v>39</v>
+      </c>
+      <c r="L42">
+        <v>0.105</v>
+      </c>
+      <c r="M42" t="s">
+        <v>40</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0.8</v>
+      </c>
+      <c r="P42">
+        <v>1.12</v>
+      </c>
+      <c r="Q42">
+        <v>20000000</v>
+      </c>
+      <c r="R42">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C43">
+        <v>13000000</v>
+      </c>
+      <c r="D43">
+        <v>12610000</v>
+      </c>
+      <c r="E43" t="s">
+        <v>26</v>
+      </c>
+      <c r="F43" t="s">
+        <v>30</v>
+      </c>
+      <c r="G43" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43">
+        <v>650</v>
+      </c>
+      <c r="K43" t="s">
+        <v>39</v>
+      </c>
+      <c r="L43">
+        <v>0.105</v>
+      </c>
+      <c r="M43" t="s">
+        <v>41</v>
+      </c>
+      <c r="N43">
+        <v>15</v>
+      </c>
+      <c r="O43">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P43">
+        <v>1.09</v>
+      </c>
+      <c r="Q43">
+        <v>20000000</v>
+      </c>
+      <c r="R43">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C44">
+        <v>13000000</v>
+      </c>
+      <c r="D44">
+        <v>12610000</v>
+      </c>
+      <c r="E44" t="s">
+        <v>26</v>
+      </c>
+      <c r="F44" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" t="s">
+        <v>36</v>
+      </c>
+      <c r="I44" t="s">
+        <v>37</v>
+      </c>
+      <c r="J44">
+        <v>650</v>
+      </c>
+      <c r="K44" t="s">
+        <v>39</v>
+      </c>
+      <c r="L44">
+        <v>0.105</v>
+      </c>
+      <c r="M44" t="s">
+        <v>41</v>
+      </c>
+      <c r="N44">
+        <v>15</v>
+      </c>
+      <c r="O44">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P44">
+        <v>1.06</v>
+      </c>
+      <c r="Q44">
+        <v>20000000</v>
+      </c>
+      <c r="R44">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C45">
+        <v>13000000</v>
+      </c>
+      <c r="D45">
+        <v>12610000</v>
+      </c>
+      <c r="E45" t="s">
+        <v>26</v>
+      </c>
+      <c r="F45" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" t="s">
+        <v>36</v>
+      </c>
+      <c r="I45" t="s">
+        <v>37</v>
+      </c>
+      <c r="J45">
+        <v>650</v>
+      </c>
+      <c r="K45" t="s">
+        <v>39</v>
+      </c>
+      <c r="L45">
+        <v>0.105</v>
+      </c>
+      <c r="M45" t="s">
+        <v>41</v>
+      </c>
+      <c r="N45">
+        <v>15</v>
+      </c>
+      <c r="O45">
+        <v>0.82</v>
+      </c>
+      <c r="P45">
+        <v>1.03</v>
+      </c>
+      <c r="Q45">
+        <v>20000000</v>
+      </c>
+      <c r="R45">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C46">
+        <v>13120000</v>
+      </c>
+      <c r="D46">
+        <v>12332800</v>
+      </c>
+      <c r="E46" t="s">
+        <v>26</v>
+      </c>
+      <c r="F46" t="s">
+        <v>30</v>
+      </c>
+      <c r="G46" t="s">
+        <v>34</v>
+      </c>
+      <c r="H46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" t="s">
+        <v>37</v>
+      </c>
+      <c r="J46">
+        <v>650</v>
+      </c>
+      <c r="K46" t="s">
+        <v>39</v>
+      </c>
+      <c r="L46">
+        <v>0.105</v>
+      </c>
+      <c r="M46" t="s">
+        <v>41</v>
+      </c>
+      <c r="N46">
+        <v>45</v>
+      </c>
+      <c r="O46">
+        <v>0.83</v>
+      </c>
+      <c r="P46">
+        <v>1</v>
+      </c>
+      <c r="Q46">
+        <v>20000000</v>
+      </c>
+      <c r="R46">
+        <v>6880000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C47">
+        <v>13240000</v>
+      </c>
+      <c r="D47">
+        <v>12445600</v>
+      </c>
+      <c r="E47" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" t="s">
+        <v>30</v>
+      </c>
+      <c r="G47" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" t="s">
+        <v>36</v>
+      </c>
+      <c r="I47" t="s">
+        <v>37</v>
+      </c>
+      <c r="J47">
+        <v>650</v>
+      </c>
+      <c r="K47" t="s">
+        <v>39</v>
+      </c>
+      <c r="L47">
+        <v>0.105</v>
+      </c>
+      <c r="M47" t="s">
+        <v>41</v>
+      </c>
+      <c r="N47">
+        <v>45</v>
+      </c>
+      <c r="O47">
+        <v>0.84</v>
+      </c>
+      <c r="P47">
+        <v>0.96</v>
+      </c>
+      <c r="Q47">
+        <v>20000000</v>
+      </c>
+      <c r="R47">
+        <v>6760000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C48">
+        <v>13360000</v>
+      </c>
+      <c r="D48">
+        <v>12558400</v>
+      </c>
+      <c r="E48" t="s">
+        <v>26</v>
+      </c>
+      <c r="F48" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" t="s">
+        <v>34</v>
+      </c>
+      <c r="H48" t="s">
+        <v>36</v>
+      </c>
+      <c r="I48" t="s">
+        <v>37</v>
+      </c>
+      <c r="J48">
+        <v>650</v>
+      </c>
+      <c r="K48" t="s">
+        <v>39</v>
+      </c>
+      <c r="L48">
+        <v>0.105</v>
+      </c>
+      <c r="M48" t="s">
+        <v>41</v>
+      </c>
+      <c r="N48">
+        <v>75</v>
+      </c>
+      <c r="O48">
+        <v>0.85</v>
+      </c>
+      <c r="P48">
+        <v>0.93</v>
+      </c>
+      <c r="Q48">
+        <v>20000000</v>
+      </c>
+      <c r="R48">
+        <v>6640000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C49">
+        <v>13480000</v>
+      </c>
+      <c r="D49">
+        <v>12671200</v>
+      </c>
+      <c r="E49" t="s">
+        <v>26</v>
+      </c>
+      <c r="F49" t="s">
+        <v>30</v>
+      </c>
+      <c r="G49" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" t="s">
+        <v>36</v>
+      </c>
+      <c r="I49" t="s">
+        <v>37</v>
+      </c>
+      <c r="J49">
+        <v>650</v>
+      </c>
+      <c r="K49" t="s">
+        <v>39</v>
+      </c>
+      <c r="L49">
+        <v>0.105</v>
+      </c>
+      <c r="M49" t="s">
+        <v>41</v>
+      </c>
+      <c r="N49">
+        <v>75</v>
+      </c>
+      <c r="O49">
+        <v>0.86</v>
+      </c>
+      <c r="P49">
+        <v>0.9</v>
+      </c>
+      <c r="Q49">
+        <v>20000000</v>
+      </c>
+      <c r="R49">
+        <v>6520000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="2">
+        <v>45322</v>
+      </c>
+      <c r="C50">
+        <v>21750000</v>
+      </c>
+      <c r="D50">
+        <v>21750000</v>
+      </c>
+      <c r="E50" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G50" t="s">
+        <v>35</v>
+      </c>
+      <c r="H50" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" t="s">
+        <v>38</v>
+      </c>
+      <c r="J50">
         <v>500</v>
       </c>
-      <c r="L6">
+      <c r="L50">
         <v>0.09</v>
       </c>
-      <c r="M6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
+      <c r="M50" t="s">
+        <v>40</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0.61</v>
+      </c>
+      <c r="P50">
+        <v>1.8</v>
+      </c>
+      <c r="Q50">
+        <v>22000000</v>
+      </c>
+      <c r="R50">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="A51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" s="2">
+        <v>45351</v>
+      </c>
+      <c r="C51">
+        <v>21500000</v>
+      </c>
+      <c r="D51">
+        <v>21500000</v>
+      </c>
+      <c r="E51" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51" t="s">
+        <v>27</v>
+      </c>
+      <c r="G51" t="s">
+        <v>35</v>
+      </c>
+      <c r="H51" t="s">
+        <v>36</v>
+      </c>
+      <c r="I51" t="s">
+        <v>38</v>
+      </c>
+      <c r="J51">
+        <v>500</v>
+      </c>
+      <c r="L51">
+        <v>0.09</v>
+      </c>
+      <c r="M51" t="s">
+        <v>40</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0.62</v>
+      </c>
+      <c r="P51">
+        <v>1.8</v>
+      </c>
+      <c r="Q51">
+        <v>22000000</v>
+      </c>
+      <c r="R51">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
+      <c r="A52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" s="2">
+        <v>45382</v>
+      </c>
+      <c r="C52">
+        <v>21250000</v>
+      </c>
+      <c r="D52">
+        <v>21250000</v>
+      </c>
+      <c r="E52" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" t="s">
+        <v>27</v>
+      </c>
+      <c r="G52" t="s">
+        <v>35</v>
+      </c>
+      <c r="H52" t="s">
+        <v>36</v>
+      </c>
+      <c r="I52" t="s">
+        <v>38</v>
+      </c>
+      <c r="J52">
+        <v>500</v>
+      </c>
+      <c r="L52">
+        <v>0.09</v>
+      </c>
+      <c r="M52" t="s">
+        <v>40</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0.62</v>
+      </c>
+      <c r="P52">
+        <v>1.81</v>
+      </c>
+      <c r="Q52">
+        <v>22000000</v>
+      </c>
+      <c r="R52">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
+      <c r="A53" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="2">
+        <v>45412</v>
+      </c>
+      <c r="C53">
+        <v>21000000</v>
+      </c>
+      <c r="D53">
+        <v>21000000</v>
+      </c>
+      <c r="E53" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53" t="s">
+        <v>27</v>
+      </c>
+      <c r="G53" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53" t="s">
+        <v>36</v>
+      </c>
+      <c r="I53" t="s">
+        <v>38</v>
+      </c>
+      <c r="J53">
+        <v>500</v>
+      </c>
+      <c r="L53">
+        <v>0.09</v>
+      </c>
+      <c r="M53" t="s">
+        <v>40</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0.63</v>
+      </c>
+      <c r="P53">
+        <v>1.81</v>
+      </c>
+      <c r="Q53">
+        <v>22000000</v>
+      </c>
+      <c r="R53">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
+      <c r="A54" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="2">
+        <v>45443</v>
+      </c>
+      <c r="C54">
+        <v>20750000</v>
+      </c>
+      <c r="D54">
+        <v>20750000</v>
+      </c>
+      <c r="E54" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54" t="s">
+        <v>27</v>
+      </c>
+      <c r="G54" t="s">
+        <v>35</v>
+      </c>
+      <c r="H54" t="s">
+        <v>36</v>
+      </c>
+      <c r="I54" t="s">
+        <v>38</v>
+      </c>
+      <c r="J54">
+        <v>500</v>
+      </c>
+      <c r="L54">
+        <v>0.09</v>
+      </c>
+      <c r="M54" t="s">
+        <v>40</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0.63</v>
+      </c>
+      <c r="P54">
+        <v>1.82</v>
+      </c>
+      <c r="Q54">
+        <v>22000000</v>
+      </c>
+      <c r="R54">
+        <v>1250000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
+      <c r="A55" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" s="2">
+        <v>45473</v>
+      </c>
+      <c r="C55">
+        <v>20500000</v>
+      </c>
+      <c r="D55">
+        <v>20500000</v>
+      </c>
+      <c r="E55" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" t="s">
+        <v>27</v>
+      </c>
+      <c r="G55" t="s">
+        <v>35</v>
+      </c>
+      <c r="H55" t="s">
+        <v>36</v>
+      </c>
+      <c r="I55" t="s">
+        <v>38</v>
+      </c>
+      <c r="J55">
+        <v>500</v>
+      </c>
+      <c r="L55">
+        <v>0.09</v>
+      </c>
+      <c r="M55" t="s">
+        <v>40</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0.63</v>
+      </c>
+      <c r="P55">
+        <v>1.83</v>
+      </c>
+      <c r="Q55">
+        <v>22000000</v>
+      </c>
+      <c r="R55">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18">
+      <c r="A56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="2">
+        <v>45504</v>
+      </c>
+      <c r="C56">
+        <v>19450000</v>
+      </c>
+      <c r="D56">
+        <v>19450000</v>
+      </c>
+      <c r="E56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F56" t="s">
+        <v>27</v>
+      </c>
+      <c r="G56" t="s">
+        <v>35</v>
+      </c>
+      <c r="H56" t="s">
+        <v>36</v>
+      </c>
+      <c r="I56" t="s">
+        <v>38</v>
+      </c>
+      <c r="J56">
+        <v>500</v>
+      </c>
+      <c r="L56">
+        <v>0.09</v>
+      </c>
+      <c r="M56" t="s">
+        <v>40</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0.63</v>
+      </c>
+      <c r="P56">
+        <v>1.85</v>
+      </c>
+      <c r="Q56">
+        <v>22000000</v>
+      </c>
+      <c r="R56">
+        <v>2550000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
+      <c r="A57" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45535</v>
+      </c>
+      <c r="C57">
+        <v>19200000</v>
+      </c>
+      <c r="D57">
+        <v>19200000</v>
+      </c>
+      <c r="E57" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57" t="s">
+        <v>27</v>
+      </c>
+      <c r="G57" t="s">
+        <v>35</v>
+      </c>
+      <c r="H57" t="s">
+        <v>36</v>
+      </c>
+      <c r="I57" t="s">
+        <v>38</v>
+      </c>
+      <c r="J57">
+        <v>500</v>
+      </c>
+      <c r="L57">
+        <v>0.09</v>
+      </c>
+      <c r="M57" t="s">
+        <v>40</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0.62</v>
+      </c>
+      <c r="P57">
+        <v>1.86</v>
+      </c>
+      <c r="Q57">
+        <v>22000000</v>
+      </c>
+      <c r="R57">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
+      <c r="A58" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" s="2">
+        <v>45565</v>
+      </c>
+      <c r="C58">
+        <v>18950000</v>
+      </c>
+      <c r="D58">
+        <v>18950000</v>
+      </c>
+      <c r="E58" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58" t="s">
+        <v>27</v>
+      </c>
+      <c r="G58" t="s">
+        <v>35</v>
+      </c>
+      <c r="H58" t="s">
+        <v>36</v>
+      </c>
+      <c r="I58" t="s">
+        <v>38</v>
+      </c>
+      <c r="J58">
+        <v>500</v>
+      </c>
+      <c r="L58">
+        <v>0.09</v>
+      </c>
+      <c r="M58" t="s">
+        <v>40</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0.62</v>
+      </c>
+      <c r="P58">
+        <v>1.87</v>
+      </c>
+      <c r="Q58">
+        <v>22000000</v>
+      </c>
+      <c r="R58">
+        <v>3050000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
+      <c r="A59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="2">
+        <v>45596</v>
+      </c>
+      <c r="C59">
+        <v>18700000</v>
+      </c>
+      <c r="D59">
+        <v>18700000</v>
+      </c>
+      <c r="E59" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59" t="s">
+        <v>27</v>
+      </c>
+      <c r="G59" t="s">
+        <v>35</v>
+      </c>
+      <c r="H59" t="s">
+        <v>36</v>
+      </c>
+      <c r="I59" t="s">
+        <v>38</v>
+      </c>
+      <c r="J59">
+        <v>500</v>
+      </c>
+      <c r="L59">
+        <v>0.09</v>
+      </c>
+      <c r="M59" t="s">
+        <v>40</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0.61</v>
+      </c>
+      <c r="P59">
+        <v>1.88</v>
+      </c>
+      <c r="Q59">
+        <v>22000000</v>
+      </c>
+      <c r="R59">
+        <v>3300000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="A60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C60">
+        <v>18450000</v>
+      </c>
+      <c r="D60">
+        <v>18450000</v>
+      </c>
+      <c r="E60" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60" t="s">
+        <v>27</v>
+      </c>
+      <c r="G60" t="s">
+        <v>35</v>
+      </c>
+      <c r="H60" t="s">
+        <v>36</v>
+      </c>
+      <c r="I60" t="s">
+        <v>38</v>
+      </c>
+      <c r="J60">
+        <v>500</v>
+      </c>
+      <c r="L60">
+        <v>0.09</v>
+      </c>
+      <c r="M60" t="s">
+        <v>40</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0.61</v>
+      </c>
+      <c r="P60">
+        <v>1.89</v>
+      </c>
+      <c r="Q60">
+        <v>22000000</v>
+      </c>
+      <c r="R60">
+        <v>3550000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
+      <c r="A61" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="2">
+        <v>45657</v>
+      </c>
+      <c r="C61">
+        <v>18200000</v>
+      </c>
+      <c r="D61">
+        <v>18200000</v>
+      </c>
+      <c r="E61" t="s">
+        <v>23</v>
+      </c>
+      <c r="F61" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" t="s">
+        <v>35</v>
+      </c>
+      <c r="H61" t="s">
+        <v>36</v>
+      </c>
+      <c r="I61" t="s">
+        <v>38</v>
+      </c>
+      <c r="J61">
+        <v>500</v>
+      </c>
+      <c r="L61">
+        <v>0.09</v>
+      </c>
+      <c r="M61" t="s">
+        <v>40</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
         <v>0.6</v>
       </c>
-      <c r="P6">
-        <v>1.75</v>
+      <c r="P61">
+        <v>1.9</v>
+      </c>
+      <c r="Q61">
+        <v>22000000</v>
+      </c>
+      <c r="R61">
+        <v>3800000</v>
       </c>
     </row>
   </sheetData>

--- a/data/positions.xlsx
+++ b/data/positions.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codes\Python\PyCharm Projects\private-credit-performance\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4EA2AB-0858-4850-A1A8-05A82A4F176E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="48">
   <si>
     <t>loan_id</t>
   </si>
@@ -68,6 +87,24 @@
   </si>
   <si>
     <t>undrawn</t>
+  </si>
+  <si>
+    <t>collateral_mv</t>
+  </si>
+  <si>
+    <t>haircut_pct</t>
+  </si>
+  <si>
+    <t>advance_rate_pct</t>
+  </si>
+  <si>
+    <t>eligible_flag</t>
+  </si>
+  <si>
+    <t>eligible_collateral</t>
+  </si>
+  <si>
+    <t>borrowing_base_contrib</t>
   </si>
   <si>
     <t>L001</t>
@@ -145,11 +182,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +198,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -198,28 +244,42 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -257,7 +317,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -291,6 +351,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -325,9 +386,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -500,11 +562,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:X61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,46 +644,64 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2">
         <v>45322</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>20000000</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>20000000</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J2">
         <v>450</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L2">
-        <v>0.08499999999999999</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -609,52 +712,70 @@
       <c r="P2">
         <v>1.85</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="3">
         <v>30000000</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="3">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="3" spans="1:18">
+      <c r="S2">
+        <v>28571428.571428571</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2" s="3">
+        <v>25714285.71428572</v>
+      </c>
+      <c r="X2" s="3">
+        <v>18000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2">
         <v>45351</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>23000000</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>23000000</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J3">
         <v>450</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L3">
-        <v>0.08499999999999999</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -665,52 +786,70 @@
       <c r="P3">
         <v>1.85</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="3">
         <v>30000000</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="3">
         <v>7000000</v>
       </c>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="S3">
+        <v>32857142.857142858</v>
+      </c>
+      <c r="T3" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U3" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3" s="3">
+        <v>29571428.571428571</v>
+      </c>
+      <c r="X3" s="3">
+        <v>20700000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2">
         <v>45382</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>23000000</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>23000000</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J4">
         <v>450</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L4">
-        <v>0.08499999999999999</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -721,52 +860,70 @@
       <c r="P4">
         <v>1.86</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="3">
         <v>30000000</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="3">
         <v>7000000</v>
       </c>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="S4">
+        <v>32857142.857142858</v>
+      </c>
+      <c r="T4" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U4" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4" s="3">
+        <v>29571428.571428571</v>
+      </c>
+      <c r="X4" s="3">
+        <v>20700000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B5" s="2">
         <v>45412</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>24000000</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>24000000</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J5">
         <v>450</v>
       </c>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L5">
-        <v>0.08499999999999999</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -777,52 +934,70 @@
       <c r="P5">
         <v>1.86</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="3">
         <v>30000000</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="3">
         <v>6000000</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="S5">
+        <v>34285714.285714291</v>
+      </c>
+      <c r="T5" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U5" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5" s="3">
+        <v>30857142.857142858</v>
+      </c>
+      <c r="X5" s="3">
+        <v>21600000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2">
         <v>45443</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="3">
         <v>25000000</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
         <v>25000000</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J6">
         <v>450</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L6">
-        <v>0.08499999999999999</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -833,52 +1008,70 @@
       <c r="P6">
         <v>1.87</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="3">
         <v>30000000</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="3">
         <v>5000000</v>
       </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="S6">
+        <v>35714285.714285716</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U6" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6" s="3">
+        <v>32142857.142857149</v>
+      </c>
+      <c r="X6" s="3">
+        <v>22500000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>45473</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>25000000</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>25000000</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J7">
         <v>450</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L7">
-        <v>0.08499999999999999</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M7" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -889,52 +1082,70 @@
       <c r="P7">
         <v>1.88</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="3">
         <v>30000000</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="3">
         <v>5000000</v>
       </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="S7">
+        <v>35714285.714285716</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U7" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7" s="3">
+        <v>32142857.142857149</v>
+      </c>
+      <c r="X7" s="3">
+        <v>22500000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B8" s="2">
         <v>45504</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>24800000</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="3">
         <v>24800000</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J8">
         <v>450</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L8">
-        <v>0.08499999999999999</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M8" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -945,52 +1156,70 @@
       <c r="P8">
         <v>1.9</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="3">
         <v>30000000</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="3">
         <v>5200000</v>
       </c>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="S8">
+        <v>35428571.428571433</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8" s="3">
+        <v>31885714.285714291</v>
+      </c>
+      <c r="X8" s="3">
+        <v>22320000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2">
         <v>45535</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <v>24600000</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="3">
         <v>24600000</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J9">
         <v>450</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L9">
-        <v>0.08499999999999999</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -1001,52 +1230,70 @@
       <c r="P9">
         <v>1.91</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="3">
         <v>30000000</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="3">
         <v>5400000</v>
       </c>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="S9">
+        <v>35142857.142857142</v>
+      </c>
+      <c r="T9" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U9" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9" s="3">
+        <v>31628571.428571429</v>
+      </c>
+      <c r="X9" s="3">
+        <v>22140000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2">
         <v>45565</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="3">
         <v>24400000</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="3">
         <v>24400000</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J10">
         <v>450</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L10">
-        <v>0.08499999999999999</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M10" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -1057,52 +1304,70 @@
       <c r="P10">
         <v>1.92</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="3">
         <v>30000000</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="3">
         <v>5600000</v>
       </c>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="S10">
+        <v>34857142.857142858</v>
+      </c>
+      <c r="T10" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U10" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10" s="3">
+        <v>31371428.571428571</v>
+      </c>
+      <c r="X10" s="3">
+        <v>21960000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2">
         <v>45596</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="3">
         <v>23200000</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="3">
         <v>23200000</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J11">
         <v>450</v>
       </c>
       <c r="K11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L11">
-        <v>0.08499999999999999</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1113,52 +1378,70 @@
       <c r="P11">
         <v>1.93</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="3">
         <v>30000000</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="3">
         <v>6800000</v>
       </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="S11">
+        <v>33142857.142857149</v>
+      </c>
+      <c r="T11" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U11" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11" s="3">
+        <v>29828571.428571429</v>
+      </c>
+      <c r="X11" s="3">
+        <v>20880000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2">
         <v>45626</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>23000000</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="3">
         <v>23000000</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I12" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J12">
         <v>450</v>
       </c>
       <c r="K12" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L12">
-        <v>0.08499999999999999</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M12" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -1169,52 +1452,70 @@
       <c r="P12">
         <v>1.94</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="3">
         <v>30000000</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="3">
         <v>7000000</v>
       </c>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="S12">
+        <v>32857142.857142858</v>
+      </c>
+      <c r="T12" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U12" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12" s="3">
+        <v>29571428.571428571</v>
+      </c>
+      <c r="X12" s="3">
+        <v>20700000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2">
         <v>45657</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="3">
         <v>22800000</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="3">
         <v>22800000</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J13">
         <v>450</v>
       </c>
       <c r="K13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L13">
-        <v>0.08499999999999999</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M13" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -1225,52 +1526,70 @@
       <c r="P13">
         <v>1.95</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="3">
         <v>30000000</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="3">
         <v>7200000</v>
       </c>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="S13">
+        <v>32571428.571428571</v>
+      </c>
+      <c r="T13" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U13" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13" s="3">
+        <v>29314285.71428572</v>
+      </c>
+      <c r="X13" s="3">
+        <v>20520000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2">
         <v>45322</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="3">
         <v>13000000</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="3">
         <v>13000000</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J14">
         <v>525</v>
       </c>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L14">
-        <v>0.0925</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -1281,52 +1600,70 @@
       <c r="P14">
         <v>1.5</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="3">
         <v>25000000</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="3">
         <v>12000000</v>
       </c>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="S14">
+        <v>19117647.05882353</v>
+      </c>
+      <c r="T14" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="U14" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14" s="3">
+        <v>16823529.411764711</v>
+      </c>
+      <c r="X14" s="3">
+        <v>11440000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2">
         <v>45351</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="3">
         <v>13000000</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="3">
         <v>13000000</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I15" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J15">
         <v>525</v>
       </c>
       <c r="K15" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L15">
-        <v>0.0925</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M15" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -1337,52 +1674,70 @@
       <c r="P15">
         <v>1.5</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="3">
         <v>25000000</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="3">
         <v>12000000</v>
       </c>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="S15">
+        <v>19092626.287892058</v>
+      </c>
+      <c r="T15" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="U15" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15" s="3">
+        <v>16801511.133345012</v>
+      </c>
+      <c r="X15" s="3">
+        <v>11425027.570674609</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2">
         <v>45382</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="3">
         <v>16000000</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="3">
         <v>16000000</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H16" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I16" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J16">
         <v>525</v>
       </c>
       <c r="K16" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L16">
-        <v>0.0925</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M16" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -1393,52 +1748,70 @@
       <c r="P16">
         <v>1.51</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="3">
         <v>25000000</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="3">
         <v>9000000</v>
       </c>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="S16">
+        <v>23471212.25382873</v>
+      </c>
+      <c r="T16" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16" s="3">
+        <v>20654666.78336928</v>
+      </c>
+      <c r="X16" s="3">
+        <v>14045173.412691111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2">
         <v>45412</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="3">
         <v>16000000</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="3">
         <v>16000000</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I17" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J17">
         <v>525</v>
       </c>
       <c r="K17" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L17">
-        <v>0.0925</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M17" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -1449,52 +1822,70 @@
       <c r="P17">
         <v>1.51</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="3">
         <v>25000000</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="3">
         <v>9000000</v>
       </c>
-    </row>
-    <row r="18" spans="1:18">
+      <c r="S17">
+        <v>23450214.495547488</v>
+      </c>
+      <c r="T17" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="U17" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17" s="3">
+        <v>20636188.75608179</v>
+      </c>
+      <c r="X17" s="3">
+        <v>14032608.354135619</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2">
         <v>45443</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="3">
         <v>18000000</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="3">
         <v>18000000</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H18" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I18" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J18">
         <v>525</v>
       </c>
       <c r="K18" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L18">
-        <v>0.0925</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M18" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -1505,52 +1896,70 @@
       <c r="P18">
         <v>1.52</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="3">
         <v>25000000</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="3">
         <v>7000000</v>
       </c>
-    </row>
-    <row r="19" spans="1:18">
+      <c r="S18">
+        <v>26367677.16338506</v>
+      </c>
+      <c r="T18" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="U18" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18" s="3">
+        <v>23203555.903778851</v>
+      </c>
+      <c r="X18" s="3">
+        <v>15778418.01456962</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2">
         <v>45473</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="3">
         <v>18060000</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="3">
         <v>17518200</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H19" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I19" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J19">
         <v>525</v>
       </c>
       <c r="K19" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L19">
-        <v>0.0925</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M19" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N19">
         <v>15</v>
@@ -1561,52 +1970,70 @@
       <c r="P19">
         <v>1.53</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="3">
         <v>25000000</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="3">
         <v>6940000</v>
       </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="S19">
+        <v>25390723.131076481</v>
+      </c>
+      <c r="T19" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="U19" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19" s="3">
+        <v>21582114.661415011</v>
+      </c>
+      <c r="X19" s="3">
+        <v>14675837.96976221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2">
         <v>45504</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="3">
         <v>18120000</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="3">
         <v>17576400</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H20" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I20" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J20">
         <v>525</v>
       </c>
       <c r="K20" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L20">
-        <v>0.0925</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M20" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N20">
         <v>15</v>
@@ -1617,52 +2044,70 @@
       <c r="P20">
         <v>1.55</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="3">
         <v>25000000</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="3">
         <v>6880000</v>
       </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="S20">
+        <v>25484256.062505409</v>
+      </c>
+      <c r="T20" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="U20" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20" s="3">
+        <v>21661617.653129589</v>
+      </c>
+      <c r="X20" s="3">
+        <v>14729900.004128121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2">
         <v>45535</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="3">
         <v>18030000</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="3">
         <v>17489100</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I21" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J21">
         <v>525</v>
       </c>
       <c r="K21" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L21">
-        <v>0.0925</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M21" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N21">
         <v>15</v>
@@ -1673,52 +2118,70 @@
       <c r="P21">
         <v>1.56</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="3">
         <v>25000000</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="3">
         <v>6970000</v>
       </c>
-    </row>
-    <row r="22" spans="1:18">
+      <c r="S21">
+        <v>25377428.009130929</v>
+      </c>
+      <c r="T21" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="U21" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21" s="3">
+        <v>21570813.807761289</v>
+      </c>
+      <c r="X21" s="3">
+        <v>14668153.38927768</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2">
         <v>45565</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="3">
         <v>17880000</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="3">
         <v>17880000</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H22" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I22" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J22">
         <v>525</v>
       </c>
       <c r="K22" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L22">
-        <v>0.0925</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M22" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -1729,52 +2192,70 @@
       <c r="P22">
         <v>1.57</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="3">
         <v>25000000</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="3">
         <v>7120000</v>
       </c>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="S22">
+        <v>26246023.32609266</v>
+      </c>
+      <c r="T22" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="U22" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22" s="3">
+        <v>23096500.526961539</v>
+      </c>
+      <c r="X22" s="3">
+        <v>15705620.35833385</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2">
         <v>45596</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="3">
         <v>17730000</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="3">
         <v>17730000</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F23" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H23" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I23" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J23">
         <v>525</v>
       </c>
       <c r="K23" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L23">
-        <v>0.0925</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M23" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -1785,52 +2266,70 @@
       <c r="P23">
         <v>1.58</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="3">
         <v>25000000</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="3">
         <v>7270000</v>
       </c>
-    </row>
-    <row r="24" spans="1:18">
+      <c r="S23">
+        <v>26058811.42504175</v>
+      </c>
+      <c r="T23" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="U23" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23" s="3">
+        <v>22931754.05403674</v>
+      </c>
+      <c r="X23" s="3">
+        <v>15593592.75674499</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2">
         <v>45626</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="3">
         <v>17580000</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="3">
         <v>17580000</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G24" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H24" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J24">
         <v>525</v>
       </c>
       <c r="K24" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L24">
-        <v>0.0925</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M24" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -1841,105 +2340,141 @@
       <c r="P24">
         <v>1.59</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="3">
         <v>25000000</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="3">
         <v>7420000</v>
       </c>
-    </row>
-    <row r="25" spans="1:18">
+      <c r="S24">
+        <v>25852941.176470589</v>
+      </c>
+      <c r="T24" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="U24" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24" s="3">
+        <v>22750588.235294111</v>
+      </c>
+      <c r="X24" s="3">
+        <v>15470400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2">
         <v>45657</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="3">
         <v>16930000</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="3">
         <v>16930000</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J25">
         <v>525</v>
       </c>
       <c r="K25" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L25">
-        <v>0.0925</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M25" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
       <c r="O25">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="P25">
         <v>1.6</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="3">
         <v>25000000</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="3">
         <v>8070000</v>
       </c>
-    </row>
-    <row r="26" spans="1:18">
+      <c r="S25">
+        <v>24897058.823529411</v>
+      </c>
+      <c r="T25" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="U25" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+      <c r="W25" s="3">
+        <v>21909411.764705881</v>
+      </c>
+      <c r="X25" s="3">
+        <v>14898400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B26" s="2">
         <v>45322</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="3">
         <v>31500000</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="3">
         <v>31027500</v>
       </c>
       <c r="E26" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F26" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H26" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I26" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J26">
         <v>600</v>
       </c>
       <c r="L26">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M26" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -1950,49 +2485,67 @@
       <c r="P26">
         <v>2.15</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="3">
         <v>32000000</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="3">
         <v>500000</v>
       </c>
-    </row>
-    <row r="27" spans="1:18">
+      <c r="S26">
+        <v>43750000</v>
+      </c>
+      <c r="T26" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="U26" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
+      </c>
+      <c r="W26" s="3">
+        <v>38937500</v>
+      </c>
+      <c r="X26" s="3">
+        <v>28035000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2">
         <v>45351</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="3">
         <v>31000000</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="3">
         <v>30535000</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F27" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H27" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I27" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J27">
         <v>600</v>
       </c>
       <c r="L27">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M27" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -2003,49 +2556,67 @@
       <c r="P27">
         <v>2.15</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="3">
         <v>32000000</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="3">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="28" spans="1:18">
+      <c r="S27">
+        <v>43055555.55555556</v>
+      </c>
+      <c r="T27" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="U27" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="V27">
+        <v>1</v>
+      </c>
+      <c r="W27" s="3">
+        <v>38319444.444444448</v>
+      </c>
+      <c r="X27" s="3">
+        <v>27590000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2">
         <v>45382</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="3">
         <v>30500000</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="3">
         <v>30042500</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F28" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H28" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I28" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J28">
         <v>600</v>
       </c>
       <c r="L28">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M28" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -2056,49 +2627,67 @@
       <c r="P28">
         <v>2.16</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="3">
         <v>32000000</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="3">
         <v>1500000</v>
       </c>
-    </row>
-    <row r="29" spans="1:18">
+      <c r="S28">
+        <v>42361111.111111112</v>
+      </c>
+      <c r="T28" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="U28" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="V28">
+        <v>1</v>
+      </c>
+      <c r="W28" s="3">
+        <v>37701388.888888888</v>
+      </c>
+      <c r="X28" s="3">
+        <v>27145000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B29" s="2">
         <v>45412</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="3">
         <v>30000000</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="3">
         <v>29550000</v>
       </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F29" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H29" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I29" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J29">
         <v>600</v>
       </c>
       <c r="L29">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M29" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -2109,49 +2698,67 @@
       <c r="P29">
         <v>2.16</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="3">
         <v>32000000</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="3">
         <v>2000000</v>
       </c>
-    </row>
-    <row r="30" spans="1:18">
+      <c r="S29">
+        <v>41666666.666666672</v>
+      </c>
+      <c r="T29" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="U29" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="V29">
+        <v>1</v>
+      </c>
+      <c r="W29" s="3">
+        <v>37083333.333333343</v>
+      </c>
+      <c r="X29" s="3">
+        <v>26700000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B30" s="2">
         <v>45443</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="3">
         <v>29500000</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="3">
         <v>29057500</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F30" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H30" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I30" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J30">
         <v>600</v>
       </c>
       <c r="L30">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M30" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -2162,49 +2769,67 @@
       <c r="P30">
         <v>2.17</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="3">
         <v>32000000</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="3">
         <v>2500000</v>
       </c>
-    </row>
-    <row r="31" spans="1:18">
+      <c r="S30">
+        <v>40972222.222222216</v>
+      </c>
+      <c r="T30" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="U30" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="V30">
+        <v>1</v>
+      </c>
+      <c r="W30" s="3">
+        <v>36465277.777777784</v>
+      </c>
+      <c r="X30" s="3">
+        <v>26255000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B31" s="2">
         <v>45473</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="3">
         <v>29000000</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="3">
         <v>28565000</v>
       </c>
       <c r="E31" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F31" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H31" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I31" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J31">
         <v>600</v>
       </c>
       <c r="L31">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M31" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -2213,51 +2838,69 @@
         <v>0.62</v>
       </c>
       <c r="P31">
-        <v>2.18</v>
-      </c>
-      <c r="Q31">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="Q31" s="3">
         <v>32000000</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="3">
         <v>3000000</v>
       </c>
-    </row>
-    <row r="32" spans="1:18">
+      <c r="S31">
+        <v>40277777.777777784</v>
+      </c>
+      <c r="T31" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="U31" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="V31">
+        <v>1</v>
+      </c>
+      <c r="W31" s="3">
+        <v>35847222.222222216</v>
+      </c>
+      <c r="X31" s="3">
+        <v>25810000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B32" s="2">
         <v>45504</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="3">
         <v>28500000</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="3">
         <v>28072500</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F32" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H32" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I32" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J32">
         <v>600</v>
       </c>
       <c r="L32">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M32" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -2266,51 +2909,69 @@
         <v>0.62</v>
       </c>
       <c r="P32">
-        <v>2.2</v>
-      </c>
-      <c r="Q32">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q32" s="3">
         <v>32000000</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="3">
         <v>3500000</v>
       </c>
-    </row>
-    <row r="33" spans="1:18">
+      <c r="S32">
+        <v>39583333.333333343</v>
+      </c>
+      <c r="T32" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="U32" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="V32">
+        <v>1</v>
+      </c>
+      <c r="W32" s="3">
+        <v>35229166.666666672</v>
+      </c>
+      <c r="X32" s="3">
+        <v>25365000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B33" s="2">
         <v>45535</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="3">
         <v>28000000</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="3">
         <v>27580000</v>
       </c>
       <c r="E33" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F33" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H33" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I33" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J33">
         <v>600</v>
       </c>
       <c r="L33">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M33" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -2321,49 +2982,67 @@
       <c r="P33">
         <v>2.21</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="3">
         <v>32000000</v>
       </c>
-      <c r="R33">
+      <c r="R33" s="3">
         <v>4000000</v>
       </c>
-    </row>
-    <row r="34" spans="1:18">
+      <c r="S33">
+        <v>38888888.888888888</v>
+      </c>
+      <c r="T33" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="U33" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="V33">
+        <v>1</v>
+      </c>
+      <c r="W33" s="3">
+        <v>34611111.111111112</v>
+      </c>
+      <c r="X33" s="3">
+        <v>24920000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B34" s="2">
         <v>45565</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="3">
         <v>26000000</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="3">
         <v>25610000</v>
       </c>
       <c r="E34" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F34" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H34" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I34" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J34">
         <v>600</v>
       </c>
       <c r="L34">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M34" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -2372,51 +3051,69 @@
         <v>0.61</v>
       </c>
       <c r="P34">
-        <v>2.22</v>
-      </c>
-      <c r="Q34">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="Q34" s="3">
         <v>32000000</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="3">
         <v>6000000</v>
       </c>
-    </row>
-    <row r="35" spans="1:18">
+      <c r="S34">
+        <v>36111111.111111112</v>
+      </c>
+      <c r="T34" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="U34" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="V34">
+        <v>1</v>
+      </c>
+      <c r="W34" s="3">
+        <v>32138888.888888892</v>
+      </c>
+      <c r="X34" s="3">
+        <v>23140000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B35" s="2">
         <v>45596</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="3">
         <v>25500000</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="3">
         <v>25117500</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F35" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H35" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I35" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J35">
         <v>600</v>
       </c>
       <c r="L35">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M35" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -2427,49 +3124,67 @@
       <c r="P35">
         <v>2.23</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" s="3">
         <v>32000000</v>
       </c>
-      <c r="R35">
+      <c r="R35" s="3">
         <v>6500000</v>
       </c>
-    </row>
-    <row r="36" spans="1:18">
+      <c r="S35">
+        <v>35416666.666666672</v>
+      </c>
+      <c r="T35" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="U35" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="V35">
+        <v>1</v>
+      </c>
+      <c r="W35" s="3">
+        <v>31520833.33333334</v>
+      </c>
+      <c r="X35" s="3">
+        <v>22695000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B36" s="2">
         <v>45626</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="3">
         <v>25000000</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="3">
         <v>24625000</v>
       </c>
       <c r="E36" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G36" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H36" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I36" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J36">
         <v>600</v>
       </c>
       <c r="L36">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M36" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -2478,51 +3193,69 @@
         <v>0.6</v>
       </c>
       <c r="P36">
-        <v>2.24</v>
-      </c>
-      <c r="Q36">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="Q36" s="3">
         <v>32000000</v>
       </c>
-      <c r="R36">
+      <c r="R36" s="3">
         <v>7000000</v>
       </c>
-    </row>
-    <row r="37" spans="1:18">
+      <c r="S36">
+        <v>34722222.222222216</v>
+      </c>
+      <c r="T36" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="U36" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="V36">
+        <v>1</v>
+      </c>
+      <c r="W36" s="3">
+        <v>30902777.77777778</v>
+      </c>
+      <c r="X36" s="3">
+        <v>22250000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B37" s="2">
         <v>45657</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="3">
         <v>24500000</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="3">
         <v>24132500</v>
       </c>
       <c r="E37" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F37" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G37" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H37" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I37" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J37">
         <v>600</v>
       </c>
       <c r="L37">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M37" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -2533,52 +3266,70 @@
       <c r="P37">
         <v>2.25</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" s="3">
         <v>32000000</v>
       </c>
-      <c r="R37">
+      <c r="R37" s="3">
         <v>7500000</v>
       </c>
-    </row>
-    <row r="38" spans="1:18">
+      <c r="S37">
+        <v>34027777.777777784</v>
+      </c>
+      <c r="T37" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="U37" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="V37">
+        <v>1</v>
+      </c>
+      <c r="W37" s="3">
+        <v>30284722.22222222</v>
+      </c>
+      <c r="X37" s="3">
+        <v>21805000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B38" s="2">
         <v>45322</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="3">
         <v>8000000</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="3">
         <v>8000000</v>
       </c>
       <c r="E38" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F38" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G38" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H38" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I38" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J38">
         <v>650</v>
       </c>
       <c r="K38" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L38">
         <v>0.105</v>
       </c>
       <c r="M38" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -2589,52 +3340,70 @@
       <c r="P38">
         <v>1.25</v>
       </c>
-      <c r="Q38">
+      <c r="Q38" s="3">
         <v>20000000</v>
       </c>
-      <c r="R38">
+      <c r="R38" s="3">
         <v>12000000</v>
       </c>
-    </row>
-    <row r="39" spans="1:18">
+      <c r="S38">
+        <v>12160000</v>
+      </c>
+      <c r="T38" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="U38" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="V38">
+        <v>1</v>
+      </c>
+      <c r="W38" s="3">
+        <v>10336000</v>
+      </c>
+      <c r="X38" s="3">
+        <v>6718400</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B39" s="2">
         <v>45351</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="3">
         <v>10000000</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="3">
         <v>10000000</v>
       </c>
       <c r="E39" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F39" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G39" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H39" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I39" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J39">
         <v>650</v>
       </c>
       <c r="K39" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L39">
         <v>0.105</v>
       </c>
       <c r="M39" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -2645,52 +3414,70 @@
       <c r="P39">
         <v>1.22</v>
       </c>
-      <c r="Q39">
+      <c r="Q39" s="3">
         <v>20000000</v>
       </c>
-      <c r="R39">
+      <c r="R39" s="3">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="40" spans="1:18">
+      <c r="S39">
+        <v>15172027.97202797</v>
+      </c>
+      <c r="T39" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="U39" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="V39">
+        <v>1</v>
+      </c>
+      <c r="W39" s="3">
+        <v>12896223.776223769</v>
+      </c>
+      <c r="X39" s="3">
+        <v>8382545.4545454541</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B40" s="2">
         <v>45382</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="3">
         <v>12000000</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="3">
         <v>12000000</v>
       </c>
       <c r="E40" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F40" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G40" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H40" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I40" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J40">
         <v>650</v>
       </c>
       <c r="K40" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L40">
         <v>0.105</v>
       </c>
       <c r="M40" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -2701,52 +3488,70 @@
       <c r="P40">
         <v>1.19</v>
       </c>
-      <c r="Q40">
+      <c r="Q40" s="3">
         <v>20000000</v>
       </c>
-      <c r="R40">
+      <c r="R40" s="3">
         <v>8000000</v>
       </c>
-    </row>
-    <row r="41" spans="1:18">
+      <c r="S40">
+        <v>18172867.132867131</v>
+      </c>
+      <c r="T40" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="U40" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="V40">
+        <v>1</v>
+      </c>
+      <c r="W40" s="3">
+        <v>15446937.06293706</v>
+      </c>
+      <c r="X40" s="3">
+        <v>10040509.09090909</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B41" s="2">
         <v>45412</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="3">
         <v>12000000</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="3">
         <v>12000000</v>
       </c>
       <c r="E41" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G41" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H41" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I41" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J41">
         <v>650</v>
       </c>
       <c r="K41" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L41">
         <v>0.105</v>
       </c>
       <c r="M41" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -2755,54 +3560,72 @@
         <v>0.79</v>
       </c>
       <c r="P41">
-        <v>1.15</v>
-      </c>
-      <c r="Q41">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q41" s="3">
         <v>20000000</v>
       </c>
-      <c r="R41">
+      <c r="R41" s="3">
         <v>8000000</v>
       </c>
-    </row>
-    <row r="42" spans="1:18">
+      <c r="S41">
+        <v>18139300.699300699</v>
+      </c>
+      <c r="T41" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="U41" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="V41">
+        <v>1</v>
+      </c>
+      <c r="W41" s="3">
+        <v>15418405.59440559</v>
+      </c>
+      <c r="X41" s="3">
+        <v>10021963.636363629</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B42" s="2">
         <v>45443</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="3">
         <v>12000000</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="3">
         <v>12000000</v>
       </c>
       <c r="E42" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F42" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G42" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H42" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I42" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J42">
         <v>650</v>
       </c>
       <c r="K42" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L42">
         <v>0.105</v>
       </c>
       <c r="M42" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -2811,166 +3634,220 @@
         <v>0.8</v>
       </c>
       <c r="P42">
-        <v>1.12</v>
-      </c>
-      <c r="Q42">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="Q42" s="3">
         <v>20000000</v>
       </c>
-      <c r="R42">
+      <c r="R42" s="3">
         <v>8000000</v>
       </c>
-    </row>
-    <row r="43" spans="1:18">
+      <c r="S42">
+        <v>18105734.265734259</v>
+      </c>
+      <c r="T42" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="U42" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="V42">
+        <v>1</v>
+      </c>
+      <c r="W42" s="3">
+        <v>15389874.125874121</v>
+      </c>
+      <c r="X42" s="3">
+        <v>10003418.18181818</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B43" s="2">
         <v>45473</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="3">
         <v>13000000</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="3">
         <v>12610000</v>
       </c>
       <c r="E43" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F43" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G43" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H43" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I43" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J43">
         <v>650</v>
       </c>
       <c r="K43" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L43">
         <v>0.105</v>
       </c>
       <c r="M43" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N43">
         <v>15</v>
       </c>
       <c r="O43">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="P43">
-        <v>1.09</v>
-      </c>
-      <c r="Q43">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="Q43" s="3">
         <v>20000000</v>
       </c>
-      <c r="R43">
+      <c r="R43" s="3">
         <v>7000000</v>
       </c>
-    </row>
-    <row r="44" spans="1:18">
+      <c r="S43">
+        <v>18778181.81818182</v>
+      </c>
+      <c r="T43" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="U43" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="V43">
+        <v>1</v>
+      </c>
+      <c r="W43" s="3">
+        <v>15398109.09090909</v>
+      </c>
+      <c r="X43" s="3">
+        <v>10008770.90909091</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B44" s="2">
         <v>45504</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="3">
         <v>13000000</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="3">
         <v>12610000</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F44" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G44" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H44" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I44" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J44">
         <v>650</v>
       </c>
       <c r="K44" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L44">
         <v>0.105</v>
       </c>
       <c r="M44" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N44">
         <v>15</v>
       </c>
       <c r="O44">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="P44">
         <v>1.06</v>
       </c>
-      <c r="Q44">
+      <c r="Q44" s="3">
         <v>20000000</v>
       </c>
-      <c r="R44">
+      <c r="R44" s="3">
         <v>7000000</v>
       </c>
-    </row>
-    <row r="45" spans="1:18">
+      <c r="S44">
+        <v>18741818.18181818</v>
+      </c>
+      <c r="T44" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="U44" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="V44">
+        <v>1</v>
+      </c>
+      <c r="W44" s="3">
+        <v>15368290.90909091</v>
+      </c>
+      <c r="X44" s="3">
+        <v>9989389.0909090936</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B45" s="2">
         <v>45535</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="3">
         <v>13000000</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="3">
         <v>12610000</v>
       </c>
       <c r="E45" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F45" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G45" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H45" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I45" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J45">
         <v>650</v>
       </c>
       <c r="K45" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L45">
         <v>0.105</v>
       </c>
       <c r="M45" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N45">
         <v>15</v>
@@ -2981,52 +3858,70 @@
       <c r="P45">
         <v>1.03</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="3">
         <v>20000000</v>
       </c>
-      <c r="R45">
+      <c r="R45" s="3">
         <v>7000000</v>
       </c>
-    </row>
-    <row r="46" spans="1:18">
+      <c r="S45">
+        <v>18705454.545454551</v>
+      </c>
+      <c r="T45" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="U45" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="V45">
+        <v>1</v>
+      </c>
+      <c r="W45" s="3">
+        <v>15338472.72727273</v>
+      </c>
+      <c r="X45" s="3">
+        <v>9970007.2727272753</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B46" s="2">
         <v>45565</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="3">
         <v>13120000</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="3">
         <v>12332800</v>
       </c>
       <c r="E46" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F46" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G46" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H46" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I46" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J46">
         <v>650</v>
       </c>
       <c r="K46" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L46">
         <v>0.105</v>
       </c>
       <c r="M46" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N46">
         <v>45</v>
@@ -3037,52 +3932,70 @@
       <c r="P46">
         <v>1</v>
       </c>
-      <c r="Q46">
+      <c r="Q46" s="3">
         <v>20000000</v>
       </c>
-      <c r="R46">
+      <c r="R46" s="3">
         <v>6880000</v>
       </c>
-    </row>
-    <row r="47" spans="1:18">
+      <c r="S46">
+        <v>17630344.055944059</v>
+      </c>
+      <c r="T46" s="4">
+        <v>0.23</v>
+      </c>
+      <c r="U46" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B47" s="2">
         <v>45596</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="3">
         <v>13240000</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="3">
         <v>12445600</v>
       </c>
       <c r="E47" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F47" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G47" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H47" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I47" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J47">
         <v>650</v>
       </c>
       <c r="K47" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L47">
         <v>0.105</v>
       </c>
       <c r="M47" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N47">
         <v>45</v>
@@ -3093,52 +4006,70 @@
       <c r="P47">
         <v>0.96</v>
       </c>
-      <c r="Q47">
+      <c r="Q47" s="3">
         <v>20000000</v>
       </c>
-      <c r="R47">
+      <c r="R47" s="3">
         <v>6760000</v>
       </c>
-    </row>
-    <row r="48" spans="1:18">
+      <c r="S47">
+        <v>17754562.237762239</v>
+      </c>
+      <c r="T47" s="4">
+        <v>0.23</v>
+      </c>
+      <c r="U47" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B48" s="2">
         <v>45626</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="3">
         <v>13360000</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="3">
         <v>12558400</v>
       </c>
       <c r="E48" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F48" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G48" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H48" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I48" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J48">
         <v>650</v>
       </c>
       <c r="K48" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L48">
         <v>0.105</v>
       </c>
       <c r="M48" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N48">
         <v>75</v>
@@ -3149,52 +4080,70 @@
       <c r="P48">
         <v>0.93</v>
       </c>
-      <c r="Q48">
+      <c r="Q48" s="3">
         <v>20000000</v>
       </c>
-      <c r="R48">
+      <c r="R48" s="3">
         <v>6640000</v>
       </c>
-    </row>
-    <row r="49" spans="1:18">
+      <c r="S48">
+        <v>17878109.09090909</v>
+      </c>
+      <c r="T48" s="4">
+        <v>0.23</v>
+      </c>
+      <c r="U48" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B49" s="2">
         <v>45657</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="3">
         <v>13480000</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="3">
         <v>12671200</v>
       </c>
       <c r="E49" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F49" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G49" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H49" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I49" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J49">
         <v>650</v>
       </c>
       <c r="K49" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L49">
         <v>0.105</v>
       </c>
       <c r="M49" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N49">
         <v>75</v>
@@ -3205,40 +4154,58 @@
       <c r="P49">
         <v>0.9</v>
       </c>
-      <c r="Q49">
+      <c r="Q49" s="3">
         <v>20000000</v>
       </c>
-      <c r="R49">
+      <c r="R49" s="3">
         <v>6520000</v>
       </c>
-    </row>
-    <row r="50" spans="1:18">
+      <c r="S49">
+        <v>18000984.615384609</v>
+      </c>
+      <c r="T49" s="4">
+        <v>0.23</v>
+      </c>
+      <c r="U49" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B50" s="2">
         <v>45322</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="3">
         <v>21750000</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="3">
         <v>21750000</v>
       </c>
       <c r="E50" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F50" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G50" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H50" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I50" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J50">
         <v>500</v>
@@ -3247,7 +4214,7 @@
         <v>0.09</v>
       </c>
       <c r="M50" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N50">
         <v>0</v>
@@ -3258,40 +4225,58 @@
       <c r="P50">
         <v>1.8</v>
       </c>
-      <c r="Q50">
+      <c r="Q50" s="3">
         <v>22000000</v>
       </c>
-      <c r="R50">
+      <c r="R50" s="3">
         <v>250000</v>
       </c>
-    </row>
-    <row r="51" spans="1:18">
+      <c r="S50">
+        <v>31071428.571428571</v>
+      </c>
+      <c r="T50" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U50" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V50">
+        <v>1</v>
+      </c>
+      <c r="W50" s="3">
+        <v>27964285.71428572</v>
+      </c>
+      <c r="X50" s="3">
+        <v>19575000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B51" s="2">
         <v>45351</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="3">
         <v>21500000</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="3">
         <v>21500000</v>
       </c>
       <c r="E51" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F51" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G51" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H51" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I51" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J51">
         <v>500</v>
@@ -3300,7 +4285,7 @@
         <v>0.09</v>
       </c>
       <c r="M51" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N51">
         <v>0</v>
@@ -3311,40 +4296,58 @@
       <c r="P51">
         <v>1.8</v>
       </c>
-      <c r="Q51">
+      <c r="Q51" s="3">
         <v>22000000</v>
       </c>
-      <c r="R51">
+      <c r="R51" s="3">
         <v>500000</v>
       </c>
-    </row>
-    <row r="52" spans="1:18">
+      <c r="S51">
+        <v>30714285.71428572</v>
+      </c>
+      <c r="T51" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U51" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V51">
+        <v>1</v>
+      </c>
+      <c r="W51" s="3">
+        <v>27642857.142857149</v>
+      </c>
+      <c r="X51" s="3">
+        <v>19350000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B52" s="2">
         <v>45382</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="3">
         <v>21250000</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="3">
         <v>21250000</v>
       </c>
       <c r="E52" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F52" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G52" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H52" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I52" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J52">
         <v>500</v>
@@ -3353,7 +4356,7 @@
         <v>0.09</v>
       </c>
       <c r="M52" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N52">
         <v>0</v>
@@ -3364,40 +4367,58 @@
       <c r="P52">
         <v>1.81</v>
       </c>
-      <c r="Q52">
+      <c r="Q52" s="3">
         <v>22000000</v>
       </c>
-      <c r="R52">
+      <c r="R52" s="3">
         <v>750000</v>
       </c>
-    </row>
-    <row r="53" spans="1:18">
+      <c r="S52">
+        <v>30357142.857142858</v>
+      </c>
+      <c r="T52" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U52" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V52">
+        <v>1</v>
+      </c>
+      <c r="W52" s="3">
+        <v>27321428.571428571</v>
+      </c>
+      <c r="X52" s="3">
+        <v>19125000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B53" s="2">
         <v>45412</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="3">
         <v>21000000</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="3">
         <v>21000000</v>
       </c>
       <c r="E53" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F53" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G53" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H53" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I53" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J53">
         <v>500</v>
@@ -3406,7 +4427,7 @@
         <v>0.09</v>
       </c>
       <c r="M53" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N53">
         <v>0</v>
@@ -3417,40 +4438,58 @@
       <c r="P53">
         <v>1.81</v>
       </c>
-      <c r="Q53">
+      <c r="Q53" s="3">
         <v>22000000</v>
       </c>
-      <c r="R53">
+      <c r="R53" s="3">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="54" spans="1:18">
+      <c r="S53">
+        <v>30000000</v>
+      </c>
+      <c r="T53" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U53" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V53">
+        <v>1</v>
+      </c>
+      <c r="W53" s="3">
+        <v>27000000</v>
+      </c>
+      <c r="X53" s="3">
+        <v>18900000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B54" s="2">
         <v>45443</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="3">
         <v>20750000</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="3">
         <v>20750000</v>
       </c>
       <c r="E54" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F54" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H54" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I54" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J54">
         <v>500</v>
@@ -3459,7 +4498,7 @@
         <v>0.09</v>
       </c>
       <c r="M54" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N54">
         <v>0</v>
@@ -3470,40 +4509,58 @@
       <c r="P54">
         <v>1.82</v>
       </c>
-      <c r="Q54">
+      <c r="Q54" s="3">
         <v>22000000</v>
       </c>
-      <c r="R54">
+      <c r="R54" s="3">
         <v>1250000</v>
       </c>
-    </row>
-    <row r="55" spans="1:18">
+      <c r="S54">
+        <v>29642857.142857149</v>
+      </c>
+      <c r="T54" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U54" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V54">
+        <v>1</v>
+      </c>
+      <c r="W54" s="3">
+        <v>26678571.428571429</v>
+      </c>
+      <c r="X54" s="3">
+        <v>18675000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B55" s="2">
         <v>45473</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="3">
         <v>20500000</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="3">
         <v>20500000</v>
       </c>
       <c r="E55" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F55" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G55" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H55" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I55" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J55">
         <v>500</v>
@@ -3512,7 +4569,7 @@
         <v>0.09</v>
       </c>
       <c r="M55" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N55">
         <v>0</v>
@@ -3523,40 +4580,58 @@
       <c r="P55">
         <v>1.83</v>
       </c>
-      <c r="Q55">
+      <c r="Q55" s="3">
         <v>22000000</v>
       </c>
-      <c r="R55">
+      <c r="R55" s="3">
         <v>1500000</v>
       </c>
-    </row>
-    <row r="56" spans="1:18">
+      <c r="S55">
+        <v>29285714.285714291</v>
+      </c>
+      <c r="T55" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U55" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V55">
+        <v>1</v>
+      </c>
+      <c r="W55" s="3">
+        <v>26357142.857142858</v>
+      </c>
+      <c r="X55" s="3">
+        <v>18450000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B56" s="2">
         <v>45504</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="3">
         <v>19450000</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="3">
         <v>19450000</v>
       </c>
       <c r="E56" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F56" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G56" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H56" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I56" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J56">
         <v>500</v>
@@ -3565,7 +4640,7 @@
         <v>0.09</v>
       </c>
       <c r="M56" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N56">
         <v>0</v>
@@ -3576,40 +4651,58 @@
       <c r="P56">
         <v>1.85</v>
       </c>
-      <c r="Q56">
+      <c r="Q56" s="3">
         <v>22000000</v>
       </c>
-      <c r="R56">
+      <c r="R56" s="3">
         <v>2550000</v>
       </c>
-    </row>
-    <row r="57" spans="1:18">
+      <c r="S56">
+        <v>27785714.285714291</v>
+      </c>
+      <c r="T56" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U56" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V56">
+        <v>1</v>
+      </c>
+      <c r="W56" s="3">
+        <v>25007142.857142858</v>
+      </c>
+      <c r="X56" s="3">
+        <v>17505000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B57" s="2">
         <v>45535</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="3">
         <v>19200000</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="3">
         <v>19200000</v>
       </c>
       <c r="E57" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F57" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G57" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H57" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I57" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J57">
         <v>500</v>
@@ -3618,7 +4711,7 @@
         <v>0.09</v>
       </c>
       <c r="M57" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N57">
         <v>0</v>
@@ -3629,40 +4722,58 @@
       <c r="P57">
         <v>1.86</v>
       </c>
-      <c r="Q57">
+      <c r="Q57" s="3">
         <v>22000000</v>
       </c>
-      <c r="R57">
+      <c r="R57" s="3">
         <v>2800000</v>
       </c>
-    </row>
-    <row r="58" spans="1:18">
+      <c r="S57">
+        <v>27428571.428571429</v>
+      </c>
+      <c r="T57" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U57" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V57">
+        <v>1</v>
+      </c>
+      <c r="W57" s="3">
+        <v>24685714.285714291</v>
+      </c>
+      <c r="X57" s="3">
+        <v>17280000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B58" s="2">
         <v>45565</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="3">
         <v>18950000</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="3">
         <v>18950000</v>
       </c>
       <c r="E58" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F58" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H58" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I58" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J58">
         <v>500</v>
@@ -3671,7 +4782,7 @@
         <v>0.09</v>
       </c>
       <c r="M58" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N58">
         <v>0</v>
@@ -3682,40 +4793,58 @@
       <c r="P58">
         <v>1.87</v>
       </c>
-      <c r="Q58">
+      <c r="Q58" s="3">
         <v>22000000</v>
       </c>
-      <c r="R58">
+      <c r="R58" s="3">
         <v>3050000</v>
       </c>
-    </row>
-    <row r="59" spans="1:18">
+      <c r="S58">
+        <v>27071428.571428571</v>
+      </c>
+      <c r="T58" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U58" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V58">
+        <v>1</v>
+      </c>
+      <c r="W58" s="3">
+        <v>24364285.71428572</v>
+      </c>
+      <c r="X58" s="3">
+        <v>17055000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B59" s="2">
         <v>45596</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="3">
         <v>18700000</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="3">
         <v>18700000</v>
       </c>
       <c r="E59" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F59" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G59" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H59" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I59" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J59">
         <v>500</v>
@@ -3724,7 +4853,7 @@
         <v>0.09</v>
       </c>
       <c r="M59" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N59">
         <v>0</v>
@@ -3735,40 +4864,58 @@
       <c r="P59">
         <v>1.88</v>
       </c>
-      <c r="Q59">
+      <c r="Q59" s="3">
         <v>22000000</v>
       </c>
-      <c r="R59">
+      <c r="R59" s="3">
         <v>3300000</v>
       </c>
-    </row>
-    <row r="60" spans="1:18">
+      <c r="S59">
+        <v>26714285.71428572</v>
+      </c>
+      <c r="T59" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U59" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V59">
+        <v>1</v>
+      </c>
+      <c r="W59" s="3">
+        <v>24042857.142857149</v>
+      </c>
+      <c r="X59" s="3">
+        <v>16830000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B60" s="2">
         <v>45626</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="3">
         <v>18450000</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="3">
         <v>18450000</v>
       </c>
       <c r="E60" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F60" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G60" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H60" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I60" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J60">
         <v>500</v>
@@ -3777,7 +4924,7 @@
         <v>0.09</v>
       </c>
       <c r="M60" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N60">
         <v>0</v>
@@ -3788,40 +4935,58 @@
       <c r="P60">
         <v>1.89</v>
       </c>
-      <c r="Q60">
+      <c r="Q60" s="3">
         <v>22000000</v>
       </c>
-      <c r="R60">
+      <c r="R60" s="3">
         <v>3550000</v>
       </c>
-    </row>
-    <row r="61" spans="1:18">
+      <c r="S60">
+        <v>26357142.857142858</v>
+      </c>
+      <c r="T60" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U60" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V60">
+        <v>1</v>
+      </c>
+      <c r="W60" s="3">
+        <v>23721428.571428571</v>
+      </c>
+      <c r="X60" s="3">
+        <v>16605000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B61" s="2">
         <v>45657</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="3">
         <v>18200000</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="3">
         <v>18200000</v>
       </c>
       <c r="E61" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F61" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G61" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H61" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I61" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J61">
         <v>500</v>
@@ -3830,7 +4995,7 @@
         <v>0.09</v>
       </c>
       <c r="M61" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N61">
         <v>0</v>
@@ -3841,11 +5006,29 @@
       <c r="P61">
         <v>1.9</v>
       </c>
-      <c r="Q61">
+      <c r="Q61" s="3">
         <v>22000000</v>
       </c>
-      <c r="R61">
+      <c r="R61" s="3">
         <v>3800000</v>
+      </c>
+      <c r="S61">
+        <v>26000000</v>
+      </c>
+      <c r="T61" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="U61" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="V61">
+        <v>1</v>
+      </c>
+      <c r="W61" s="3">
+        <v>23400000</v>
+      </c>
+      <c r="X61" s="3">
+        <v>16380000</v>
       </c>
     </row>
   </sheetData>
